--- a/backend/data/financials_by_company/1849.HK.xlsx
+++ b/backend/data/financials_by_company/1849.HK.xlsx
@@ -652,55 +652,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-546380</v>
+        <v>39408.909815</v>
       </c>
       <c r="C2" t="n">
-        <v>0.17</v>
+        <v>0.147048</v>
       </c>
       <c r="D2" t="n">
-        <v>4761000</v>
+        <v>11630000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3214000</v>
+        <v>268000</v>
       </c>
       <c r="F2" t="n">
-        <v>-3214000</v>
+        <v>268000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1634000</v>
+        <v>7732000</v>
       </c>
       <c r="H2" t="n">
-        <v>1093000</v>
+        <v>787000</v>
       </c>
       <c r="I2" t="n">
-        <v>35109000</v>
+        <v>36528000</v>
       </c>
       <c r="J2" t="n">
-        <v>1547000</v>
+        <v>11898000</v>
       </c>
       <c r="K2" t="n">
-        <v>454000</v>
+        <v>11111000</v>
       </c>
       <c r="L2" t="n">
-        <v>6000</v>
+        <v>-54000</v>
       </c>
       <c r="M2" t="n">
-        <v>221000</v>
+        <v>67000</v>
       </c>
       <c r="N2" t="n">
-        <v>227000</v>
+        <v>13000</v>
       </c>
       <c r="O2" t="n">
-        <v>1033620</v>
+        <v>7503408.909815</v>
       </c>
       <c r="P2" t="n">
-        <v>-1634000</v>
+        <v>7732000</v>
       </c>
       <c r="Q2" t="n">
-        <v>45115000</v>
+        <v>44971000</v>
       </c>
       <c r="R2" t="n">
         <v>800000000</v>
@@ -709,83 +709,85 @@
         <v>800000000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.002</v>
+        <v>0.01</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.002</v>
+        <v>0.01</v>
       </c>
       <c r="V2" t="n">
-        <v>-1634000</v>
+        <v>7732000</v>
       </c>
       <c r="W2" t="n">
-        <v>-1634000</v>
+        <v>7732000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1634000</v>
+        <v>7732000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-553000</v>
+        <v>-1688000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1081000</v>
+        <v>9420000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1081000</v>
+        <v>9420000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1314000</v>
+        <v>1624000</v>
       </c>
       <c r="AD2" t="n">
-        <v>233000</v>
+        <v>11044000</v>
       </c>
       <c r="AE2" t="n">
-        <v>348000</v>
+        <v>280000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3214000</v>
+        <v>268000</v>
       </c>
       <c r="AG2" t="n">
-        <v>3214000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>1165000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1433000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>6000</v>
+        <v>-54000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>221000</v>
+        <v>67000</v>
       </c>
       <c r="AK2" t="n">
-        <v>227000</v>
+        <v>13000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3086000</v>
+        <v>9466000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10006000</v>
+        <v>8443000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10065000</v>
+        <v>9590000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1332000</v>
+        <v>3038000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8733000</v>
+        <v>6552000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13092000</v>
+        <v>17909000</v>
       </c>
       <c r="AR2" t="n">
-        <v>35109000</v>
+        <v>36528000</v>
       </c>
       <c r="AS2" t="n">
-        <v>48201000</v>
+        <v>54437000</v>
       </c>
       <c r="AT2" t="n">
-        <v>48201000</v>
+        <v>54437000</v>
       </c>
     </row>
     <row r="3">
@@ -930,55 +932,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>39408.909815</v>
+        <v>-546380</v>
       </c>
       <c r="C4" t="n">
-        <v>0.147048</v>
+        <v>0.17</v>
       </c>
       <c r="D4" t="n">
-        <v>11630000</v>
+        <v>4761000</v>
       </c>
       <c r="E4" t="n">
-        <v>268000</v>
+        <v>-3214000</v>
       </c>
       <c r="F4" t="n">
-        <v>268000</v>
+        <v>-3214000</v>
       </c>
       <c r="G4" t="n">
-        <v>7732000</v>
+        <v>-1634000</v>
       </c>
       <c r="H4" t="n">
-        <v>787000</v>
+        <v>1093000</v>
       </c>
       <c r="I4" t="n">
-        <v>36528000</v>
+        <v>35109000</v>
       </c>
       <c r="J4" t="n">
-        <v>11898000</v>
+        <v>1547000</v>
       </c>
       <c r="K4" t="n">
-        <v>11111000</v>
+        <v>454000</v>
       </c>
       <c r="L4" t="n">
-        <v>-54000</v>
+        <v>6000</v>
       </c>
       <c r="M4" t="n">
-        <v>67000</v>
+        <v>221000</v>
       </c>
       <c r="N4" t="n">
-        <v>13000</v>
+        <v>227000</v>
       </c>
       <c r="O4" t="n">
-        <v>7503408.909815</v>
+        <v>1033620</v>
       </c>
       <c r="P4" t="n">
-        <v>7732000</v>
+        <v>-1634000</v>
       </c>
       <c r="Q4" t="n">
-        <v>44971000</v>
+        <v>45115000</v>
       </c>
       <c r="R4" t="n">
         <v>800000000</v>
@@ -987,85 +989,83 @@
         <v>800000000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="V4" t="n">
-        <v>7732000</v>
+        <v>-1634000</v>
       </c>
       <c r="W4" t="n">
-        <v>7732000</v>
+        <v>-1634000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7732000</v>
+        <v>-1634000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1688000</v>
+        <v>-553000</v>
       </c>
       <c r="AA4" t="n">
-        <v>9420000</v>
+        <v>-1081000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9420000</v>
+        <v>-1081000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1624000</v>
+        <v>1314000</v>
       </c>
       <c r="AD4" t="n">
-        <v>11044000</v>
+        <v>233000</v>
       </c>
       <c r="AE4" t="n">
-        <v>280000</v>
+        <v>348000</v>
       </c>
       <c r="AF4" t="n">
-        <v>268000</v>
+        <v>-3214000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1433000</v>
-      </c>
+        <v>3214000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-54000</v>
+        <v>6000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67000</v>
+        <v>221000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13000</v>
+        <v>227000</v>
       </c>
       <c r="AL4" t="n">
-        <v>9466000</v>
+        <v>3086000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8443000</v>
+        <v>10006000</v>
       </c>
       <c r="AN4" t="n">
-        <v>9590000</v>
+        <v>10065000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3038000</v>
+        <v>1332000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6552000</v>
+        <v>8733000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17909000</v>
+        <v>13092000</v>
       </c>
       <c r="AR4" t="n">
-        <v>36528000</v>
+        <v>35109000</v>
       </c>
       <c r="AS4" t="n">
-        <v>54437000</v>
+        <v>48201000</v>
       </c>
       <c r="AT4" t="n">
-        <v>54437000</v>
+        <v>48201000</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>800000000</v>
@@ -1370,37 +1370,37 @@
         <v>800000000</v>
       </c>
       <c r="D2" t="n">
-        <v>3102000</v>
+        <v>3392000</v>
       </c>
       <c r="E2" t="n">
-        <v>18409000</v>
+        <v>13423000</v>
       </c>
       <c r="F2" t="n">
-        <v>34790000</v>
+        <v>37557000</v>
       </c>
       <c r="G2" t="n">
-        <v>22297000</v>
+        <v>14088000</v>
       </c>
       <c r="H2" t="n">
-        <v>18409000</v>
+        <v>13423000</v>
       </c>
       <c r="I2" t="n">
-        <v>774000</v>
+        <v>1406000</v>
       </c>
       <c r="J2" t="n">
-        <v>32462000</v>
+        <v>35571000</v>
       </c>
       <c r="K2" t="n">
-        <v>34116000</v>
+        <v>37423000</v>
       </c>
       <c r="L2" t="n">
-        <v>38412000</v>
+        <v>40510000</v>
       </c>
       <c r="M2" t="n">
-        <v>5950000</v>
+        <v>4939000</v>
       </c>
       <c r="N2" t="n">
-        <v>32462000</v>
+        <v>35571000</v>
       </c>
       <c r="O2" t="n">
         <v>19366000</v>
@@ -1412,113 +1412,121 @@
         <v>1389000</v>
       </c>
       <c r="R2" t="n">
-        <v>23835000</v>
+        <v>26377000</v>
       </c>
       <c r="S2" t="n">
-        <v>1777000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>3088000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>571000</v>
+      </c>
       <c r="U2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1774000</v>
+        <v>2517000</v>
       </c>
       <c r="W2" t="n">
-        <v>120000</v>
+        <v>665000</v>
       </c>
       <c r="X2" t="n">
-        <v>1654000</v>
+        <v>1852000</v>
       </c>
       <c r="Y2" t="n">
-        <v>22058000</v>
+        <v>23289000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1328000</v>
+        <v>875000</v>
       </c>
       <c r="AA2" t="n">
-        <v>654000</v>
+        <v>741000</v>
       </c>
       <c r="AB2" t="n">
-        <v>674000</v>
+        <v>134000</v>
       </c>
       <c r="AC2" t="n">
-        <v>15965000</v>
+        <v>15646000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1035000</v>
+        <v>377000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2880000</v>
+        <v>2466000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12050000</v>
+        <v>12803000</v>
       </c>
       <c r="AG2" t="n">
-        <v>62247000</v>
+        <v>66887000</v>
       </c>
       <c r="AH2" t="n">
-        <v>17892000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+        <v>29510000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2858000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="n">
-        <v>2806000</v>
+        <v>2830000</v>
       </c>
       <c r="AL2" t="n">
-        <v>14053000</v>
+        <v>22148000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3272000</v>
+        <v>8295000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10781000</v>
+        <v>13853000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1033000</v>
+        <v>1674000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-628000</v>
+        <v>-1274000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1661000</v>
+        <v>2948000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1033000</v>
+        <v>1674000</v>
       </c>
       <c r="AS2" t="n">
-        <v>616000</v>
+        <v>504000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1045000</v>
+        <v>2444000</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>44355000</v>
+        <v>37377000</v>
       </c>
       <c r="AW2" t="n">
-        <v>12242000</v>
+        <v>6432000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-2757000</v>
+        <v>1314000</v>
       </c>
       <c r="AY2" t="n">
-        <v>20131000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>15350000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1771000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>20131000</v>
+        <v>17121000</v>
       </c>
       <c r="BB2" t="n">
-        <v>14739000</v>
+        <v>14281000</v>
       </c>
       <c r="BC2" t="n">
-        <v>14739000</v>
+        <v>14281000</v>
       </c>
       <c r="BD2" t="n">
-        <v>14739000</v>
+        <v>14281000</v>
       </c>
     </row>
     <row r="3">
@@ -1691,7 +1699,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>800000000</v>
@@ -1700,37 +1708,37 @@
         <v>800000000</v>
       </c>
       <c r="D4" t="n">
-        <v>3392000</v>
+        <v>3102000</v>
       </c>
       <c r="E4" t="n">
-        <v>13423000</v>
+        <v>18409000</v>
       </c>
       <c r="F4" t="n">
-        <v>37557000</v>
+        <v>34790000</v>
       </c>
       <c r="G4" t="n">
-        <v>14088000</v>
+        <v>22297000</v>
       </c>
       <c r="H4" t="n">
-        <v>13423000</v>
+        <v>18409000</v>
       </c>
       <c r="I4" t="n">
-        <v>1406000</v>
+        <v>774000</v>
       </c>
       <c r="J4" t="n">
-        <v>35571000</v>
+        <v>32462000</v>
       </c>
       <c r="K4" t="n">
-        <v>37423000</v>
+        <v>34116000</v>
       </c>
       <c r="L4" t="n">
-        <v>40510000</v>
+        <v>38412000</v>
       </c>
       <c r="M4" t="n">
-        <v>4939000</v>
+        <v>5950000</v>
       </c>
       <c r="N4" t="n">
-        <v>35571000</v>
+        <v>32462000</v>
       </c>
       <c r="O4" t="n">
         <v>19366000</v>
@@ -1742,121 +1750,113 @@
         <v>1389000</v>
       </c>
       <c r="R4" t="n">
-        <v>26377000</v>
+        <v>23835000</v>
       </c>
       <c r="S4" t="n">
-        <v>3088000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>571000</v>
-      </c>
+        <v>1777000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V4" t="n">
-        <v>2517000</v>
+        <v>1774000</v>
       </c>
       <c r="W4" t="n">
-        <v>665000</v>
+        <v>120000</v>
       </c>
       <c r="X4" t="n">
-        <v>1852000</v>
+        <v>1654000</v>
       </c>
       <c r="Y4" t="n">
-        <v>23289000</v>
+        <v>22058000</v>
       </c>
       <c r="Z4" t="n">
-        <v>875000</v>
+        <v>1328000</v>
       </c>
       <c r="AA4" t="n">
-        <v>741000</v>
+        <v>654000</v>
       </c>
       <c r="AB4" t="n">
-        <v>134000</v>
+        <v>674000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15646000</v>
+        <v>15965000</v>
       </c>
       <c r="AD4" t="n">
-        <v>377000</v>
+        <v>1035000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2466000</v>
+        <v>2880000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12803000</v>
+        <v>12050000</v>
       </c>
       <c r="AG4" t="n">
-        <v>66887000</v>
+        <v>62247000</v>
       </c>
       <c r="AH4" t="n">
-        <v>29510000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2858000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>17892000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>2830000</v>
+        <v>2806000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22148000</v>
+        <v>14053000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8295000</v>
+        <v>3272000</v>
       </c>
       <c r="AN4" t="n">
-        <v>13853000</v>
+        <v>10781000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1674000</v>
+        <v>1033000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1274000</v>
+        <v>-628000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2948000</v>
+        <v>1661000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1674000</v>
+        <v>1033000</v>
       </c>
       <c r="AS4" t="n">
-        <v>504000</v>
+        <v>616000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2444000</v>
+        <v>1045000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>37377000</v>
+        <v>44355000</v>
       </c>
       <c r="AW4" t="n">
-        <v>6432000</v>
+        <v>12242000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1314000</v>
+        <v>-2757000</v>
       </c>
       <c r="AY4" t="n">
-        <v>15350000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-1771000</v>
-      </c>
+        <v>20131000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>17121000</v>
+        <v>20131000</v>
       </c>
       <c r="BB4" t="n">
-        <v>14281000</v>
+        <v>14739000</v>
       </c>
       <c r="BC4" t="n">
-        <v>14281000</v>
+        <v>14739000</v>
       </c>
       <c r="BD4" t="n">
-        <v>14281000</v>
+        <v>14739000</v>
       </c>
     </row>
   </sheetData>
@@ -2087,111 +2087,131 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-4073000</v>
+        <v>7593000</v>
       </c>
       <c r="C2" t="n">
-        <v>-646000</v>
+        <v>-128000</v>
       </c>
       <c r="D2" t="n">
-        <v>761000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-80000</v>
+        <v>-3103000</v>
       </c>
       <c r="G2" t="n">
-        <v>14739000</v>
+        <v>14281000</v>
       </c>
       <c r="H2" t="n">
-        <v>12307000</v>
+        <v>19125000</v>
       </c>
       <c r="I2" t="n">
-        <v>-379000</v>
+        <v>323000</v>
       </c>
       <c r="J2" t="n">
-        <v>2811000</v>
+        <v>-5167000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1035000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>2109000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2871000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-193000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-67000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>115000</v>
+        <v>-128000</v>
       </c>
       <c r="Q2" t="n">
-        <v>115000</v>
+        <v>-128000</v>
       </c>
       <c r="R2" t="n">
-        <v>-646000</v>
+        <v>-128000</v>
       </c>
       <c r="S2" t="n">
-        <v>761000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>7839000</v>
+        <v>-17972000</v>
       </c>
       <c r="U2" t="n">
-        <v>227000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>13000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-14882000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-14882000</v>
+      </c>
       <c r="X2" t="n">
-        <v>7692000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7692000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>-21000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-21000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-80000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>-3082000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-80000</v>
+        <v>-3082000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3993000</v>
+        <v>10696000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-485000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>-1657000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-27000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-8042000</v>
+        <v>1588000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1013000</v>
+        <v>-354000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2684000</v>
+        <v>9942000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4345000</v>
+        <v>-8000000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-6000</v>
+        <v>-1379000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1093000</v>
+        <v>787000</v>
       </c>
       <c r="AM2" t="n">
-        <v>60000</v>
+        <v>32000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1033000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>755000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1453000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>233000</v>
+        <v>11044000</v>
       </c>
     </row>
     <row r="3">
@@ -2313,131 +2333,111 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>7593000</v>
+        <v>-4073000</v>
       </c>
       <c r="C4" t="n">
-        <v>-128000</v>
+        <v>-646000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>761000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-3103000</v>
+        <v>-80000</v>
       </c>
       <c r="G4" t="n">
-        <v>14281000</v>
+        <v>14739000</v>
       </c>
       <c r="H4" t="n">
-        <v>19125000</v>
+        <v>12307000</v>
       </c>
       <c r="I4" t="n">
-        <v>323000</v>
+        <v>-379000</v>
       </c>
       <c r="J4" t="n">
-        <v>-5167000</v>
+        <v>2811000</v>
       </c>
       <c r="K4" t="n">
-        <v>2109000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2871000</v>
-      </c>
+        <v>-1035000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-67000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-193000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-128000</v>
+        <v>115000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-128000</v>
+        <v>115000</v>
       </c>
       <c r="R4" t="n">
-        <v>-128000</v>
+        <v>-646000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>761000</v>
       </c>
       <c r="T4" t="n">
-        <v>-17972000</v>
+        <v>7839000</v>
       </c>
       <c r="U4" t="n">
-        <v>13000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-14882000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-14882000</v>
-      </c>
+        <v>227000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-21000</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>-21000</v>
-      </c>
+        <v>7692000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7692000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-3082000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>-80000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-3082000</v>
+        <v>-80000</v>
       </c>
       <c r="AD4" t="n">
-        <v>10696000</v>
+        <v>-3993000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1657000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-27000</v>
-      </c>
+        <v>-485000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>1588000</v>
+        <v>-8042000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-354000</v>
+        <v>-1013000</v>
       </c>
       <c r="AI4" t="n">
-        <v>9942000</v>
+        <v>-2684000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-8000000</v>
+        <v>-4345000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1379000</v>
+        <v>-6000</v>
       </c>
       <c r="AL4" t="n">
-        <v>787000</v>
+        <v>1093000</v>
       </c>
       <c r="AM4" t="n">
-        <v>32000</v>
+        <v>60000</v>
       </c>
       <c r="AN4" t="n">
-        <v>755000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-49000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-1453000</v>
-      </c>
+        <v>1033000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>11044000</v>
+        <v>233000</v>
       </c>
     </row>
   </sheetData>
@@ -2917,152 +2917,152 @@
       </c>
       <c r="CO1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Li Lian  Teo', 'age': 45, 'title': 'Executive Chairlady &amp; CEO', 'yearBorn': 1980, 'fiscalYear': 2023, 'totalPay': 11040779, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wee Pin  Lim', 'age': 54, 'title': 'Chief Financial Officer', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 110285, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kuo Liang  Teo', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2023, 'totalPay': 10930494, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wee Chyun  Lee', 'age': 34, 'title': 'Head of Sales', 'yearBorn': 1991, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wan Ping  Wong', 'age': 38, 'title': 'Head of Digital Marketing', 'yearBorn': 1987, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ding Yuan  Tan', 'age': 41, 'title': 'Head of Customer Relations', 'yearBorn': 1984, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chun Pong  Tang', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Ling  Lam', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Li Lian  Teo', 'age': 45, 'title': 'Executive Chairlady &amp; CEO', 'yearBorn': 1980, 'fiscalYear': 2023, 'totalPay': 10925813, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wee Pin  Lim', 'age': 54, 'title': 'Chief Financial Officer', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 109137, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kuo Liang  Teo', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2023, 'totalPay': 10816676, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wee Chyun  Lee', 'age': 34, 'title': 'Head of Sales', 'yearBorn': 1991, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wan Ping  Wong', 'age': 38, 'title': 'Head of Digital Marketing', 'yearBorn': 1987, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ding Yuan  Tan', 'age': 41, 'title': 'Head of Customer Relations', 'yearBorn': 1984, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chun Pong  Tang', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Ling  Lam', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -3312,10 +3312,10 @@
         <v>800000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.018408503</v>
+        <v>0.018193217</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7161362</v>
+        <v>2.748277</v>
       </c>
       <c r="BG2" t="n">
         <v>1751241600</v>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -3439,117 +3439,117 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="CP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1561685400000</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>0.052 - 0.052</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.05 - 0.052</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.0020000003</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.038461544</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1727693940</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1727693940</v>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>AM GROUP</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>AM Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>1726454209</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>finmb_616053935</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="CS2" t="n">
+      <c r="DP2" t="n">
         <v>28800000</v>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="CU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>1726454209</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>AM Group Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>AM GROUP</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>1561685400000</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>0.052 - 0.052</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.052</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.0020000003</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.038461544</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1727693940</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1727693940</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.03</v>
+      <c r="DR2" t="b">
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
